--- a/config/CT Term Mapping Dictionary.xlsx
+++ b/config/CT Term Mapping Dictionary.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shirley.ho\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCA6656-96C8-42AC-A9D5-86AFA83108CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B8E33B-BA45-4A09-8B9A-DE8E7488E63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51DA8FFF-F53B-43BA-9BD3-FE23D4CF3F85}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51DA8FFF-F53B-43BA-9BD3-FE23D4CF3F85}"/>
   </bookViews>
   <sheets>
     <sheet name="CT Term Mapping" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CT Term Mapping'!$A$1:$C$409</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CT Term Mapping'!$A$1:$C$500</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="495">
   <si>
     <t>CTVAL</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1606,6 +1606,94 @@
   </si>
   <si>
     <t>Start Date Unknown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STENRF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Auto Basophil</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BASO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BASOLE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABSOLUTE BASOPHIL COUNT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basophils/Leukocytes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EOSLE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eosinophils/Leukocytes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LYMLE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lymphocytes/Leukocytes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONOLE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monocytes/Leukocytes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NEUTLE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neutrophils/Leukocytes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABSOLUTE EOSINOPHIL COUNT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABSOLUTE LYMPHOCYTE COUNT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABSOLUTE MONOCYTE COUNT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABSOLUTE NEUTROPHIL COUNT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HEMATOCRIT (HCT)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HEMOGLOBIN (HB)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RED BLOOD CELL (RBC)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WHITE BLOOD CELLS (WBC)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2032,7 +2120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799D48F5-B989-4AA3-BCE2-AE0AB96B6C6B}">
-  <dimension ref="A1:D477"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -3108,7 +3196,7 @@
         <v>196</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -3119,7 +3207,7 @@
         <v>196</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>196</v>
+        <v>477</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -3127,10 +3215,10 @@
         <v>50</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>56</v>
+        <v>478</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>58</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -3141,7 +3229,7 @@
         <v>56</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -3149,10 +3237,10 @@
         <v>50</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>218</v>
+        <v>56</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>218</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -3160,10 +3248,10 @@
         <v>50</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -3171,10 +3259,10 @@
         <v>50</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -3182,10 +3270,10 @@
         <v>50</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -3193,10 +3281,10 @@
         <v>50</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -3204,10 +3292,10 @@
         <v>50</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>54</v>
+        <v>226</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>54</v>
+        <v>226</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -3215,10 +3303,10 @@
         <v>50</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>228</v>
+        <v>54</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>228</v>
+        <v>54</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -3226,10 +3314,10 @@
         <v>50</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -3248,10 +3336,10 @@
         <v>50</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>230</v>
+        <v>487</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -3259,10 +3347,10 @@
         <v>50</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>260</v>
+        <v>480</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>260</v>
+        <v>198</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -3270,10 +3358,10 @@
         <v>50</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -3284,7 +3372,7 @@
         <v>260</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -3295,7 +3383,7 @@
         <v>260</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -3303,10 +3391,10 @@
         <v>50</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>298</v>
+        <v>260</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>191</v>
+        <v>263</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -3314,10 +3402,10 @@
         <v>50</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>298</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -3325,10 +3413,10 @@
         <v>50</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>439</v>
+        <v>260</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>439</v>
+        <v>493</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -3336,10 +3424,10 @@
         <v>50</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>68</v>
+        <v>298</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -3347,10 +3435,10 @@
         <v>50</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>232</v>
+        <v>298</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>232</v>
+        <v>298</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -3358,10 +3446,10 @@
         <v>50</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>234</v>
+        <v>439</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>234</v>
+        <v>439</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -3369,10 +3457,10 @@
         <v>50</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>236</v>
+        <v>68</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -3380,10 +3468,10 @@
         <v>50</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -3391,10 +3479,10 @@
         <v>50</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -3402,10 +3490,10 @@
         <v>50</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>240</v>
+        <v>491</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -3413,10 +3501,10 @@
         <v>50</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>281</v>
+        <v>492</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -3424,10 +3512,10 @@
         <v>50</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -3435,10 +3523,10 @@
         <v>50</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>281</v>
+        <v>238</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -3446,10 +3534,10 @@
         <v>50</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>281</v>
+        <v>238</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -3457,10 +3545,10 @@
         <v>50</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -3468,10 +3556,10 @@
         <v>50</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>202</v>
+        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>202</v>
+        <v>281</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -3479,10 +3567,10 @@
         <v>50</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -3490,10 +3578,10 @@
         <v>50</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>244</v>
+        <v>281</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>244</v>
+        <v>284</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -3501,10 +3589,10 @@
         <v>50</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>205</v>
+        <v>281</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>204</v>
+        <v>494</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -3512,10 +3600,10 @@
         <v>50</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>205</v>
+        <v>281</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>205</v>
+        <v>282</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -3523,10 +3611,10 @@
         <v>50</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>246</v>
+        <v>202</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>246</v>
+        <v>202</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -3534,10 +3622,10 @@
         <v>50</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>207</v>
+        <v>488</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -3545,10 +3633,10 @@
         <v>50</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>208</v>
+        <v>482</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -3556,10 +3644,10 @@
         <v>50</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -3567,10 +3655,10 @@
         <v>50</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -3578,10 +3666,10 @@
         <v>50</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -3589,10 +3677,10 @@
         <v>50</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>250</v>
+        <v>489</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -3600,10 +3688,10 @@
         <v>50</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>250</v>
+        <v>484</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>251</v>
+        <v>204</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -3611,10 +3699,10 @@
         <v>50</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>296</v>
+        <v>246</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>296</v>
+        <v>246</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -3622,10 +3710,10 @@
         <v>50</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -3633,10 +3721,10 @@
         <v>50</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>255</v>
+        <v>208</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>256</v>
+        <v>490</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -3644,10 +3732,10 @@
         <v>50</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>255</v>
+        <v>486</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>255</v>
+        <v>207</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -3655,10 +3743,10 @@
         <v>50</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>76</v>
+        <v>248</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -3666,10 +3754,10 @@
         <v>50</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>258</v>
+        <v>216</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -3677,10 +3765,10 @@
         <v>50</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>265</v>
+        <v>215</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -3688,10 +3776,10 @@
         <v>50</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -3699,10 +3787,10 @@
         <v>50</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -3710,10 +3798,10 @@
         <v>50</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -3721,10 +3809,10 @@
         <v>50</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -3732,10 +3820,10 @@
         <v>50</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>74</v>
+        <v>255</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -3743,10 +3831,10 @@
         <v>50</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -3754,10 +3842,10 @@
         <v>50</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>272</v>
+        <v>76</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>272</v>
+        <v>76</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -3765,10 +3853,10 @@
         <v>50</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -3776,10 +3864,10 @@
         <v>50</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -3787,10 +3875,10 @@
         <v>50</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -3798,10 +3886,10 @@
         <v>50</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>52</v>
+        <v>264</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>136</v>
+        <v>264</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -3809,10 +3897,10 @@
         <v>50</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>52</v>
+        <v>267</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>52</v>
+        <v>268</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -3820,10 +3908,10 @@
         <v>50</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -3831,10 +3919,10 @@
         <v>50</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>301</v>
+        <v>74</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -3842,10 +3930,10 @@
         <v>50</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -3853,10 +3941,10 @@
         <v>50</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -3864,10 +3952,10 @@
         <v>50</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -3875,10 +3963,10 @@
         <v>50</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -3886,10 +3974,10 @@
         <v>50</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -3897,10 +3985,10 @@
         <v>50</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>293</v>
+        <v>52</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>293</v>
+        <v>136</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -3908,109 +3996,109 @@
         <v>50</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>293</v>
+        <v>52</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>294</v>
+        <v>52</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>73</v>
+        <v>279</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>73</v>
+        <v>279</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>71</v>
+        <v>301</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>72</v>
+        <v>285</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>61</v>
+        <v>290</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>60</v>
+        <v>290</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>61</v>
+        <v>290</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>61</v>
+        <v>291</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>67</v>
+        <v>287</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>67</v>
+        <v>288</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>67</v>
+        <v>287</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>65</v>
+        <v>287</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>64</v>
+        <v>293</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>64</v>
+        <v>293</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>64</v>
+        <v>293</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -4018,10 +4106,10 @@
         <v>53</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -4029,10 +4117,10 @@
         <v>53</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -4040,10 +4128,10 @@
         <v>53</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>214</v>
+        <v>73</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>214</v>
+        <v>72</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -4051,10 +4139,10 @@
         <v>53</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>214</v>
+        <v>61</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>213</v>
+        <v>60</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -4062,10 +4150,10 @@
         <v>53</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>195</v>
+        <v>61</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -4073,10 +4161,10 @@
         <v>53</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>197</v>
+        <v>67</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>197</v>
+        <v>67</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -4084,10 +4172,10 @@
         <v>53</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>197</v>
+        <v>67</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>196</v>
+        <v>65</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -4095,10 +4183,10 @@
         <v>53</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -4106,10 +4194,10 @@
         <v>53</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -4117,10 +4205,10 @@
         <v>53</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>57</v>
+        <v>211</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -4128,10 +4216,10 @@
         <v>53</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -4139,10 +4227,10 @@
         <v>53</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -4150,10 +4238,10 @@
         <v>53</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -4161,10 +4249,10 @@
         <v>53</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>54</v>
+        <v>477</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -4172,10 +4260,10 @@
         <v>53</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -4183,10 +4271,10 @@
         <v>53</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>233</v>
+        <v>475</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -4194,10 +4282,10 @@
         <v>53</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>233</v>
+        <v>476</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>232</v>
+        <v>476</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -4205,10 +4293,10 @@
         <v>53</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>239</v>
+        <v>476</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>239</v>
+        <v>474</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -4216,10 +4304,10 @@
         <v>53</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>299</v>
+        <v>59</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -4227,10 +4315,10 @@
         <v>53</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>238</v>
+        <v>58</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -4238,10 +4326,10 @@
         <v>53</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>266</v>
+        <v>59</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>266</v>
+        <v>57</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -4249,10 +4337,10 @@
         <v>53</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>265</v>
+        <v>225</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -4260,10 +4348,10 @@
         <v>53</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>300</v>
+        <v>227</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -4271,10 +4359,10 @@
         <v>53</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>266</v>
+        <v>55</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>264</v>
+        <v>55</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -4282,10 +4370,10 @@
         <v>53</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>286</v>
+        <v>55</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>286</v>
+        <v>54</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -4293,10 +4381,10 @@
         <v>53</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>301</v>
+        <v>229</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -4304,10 +4392,10 @@
         <v>53</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>286</v>
+        <v>233</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>285</v>
+        <v>233</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -4315,10 +4403,10 @@
         <v>53</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -4326,10 +4414,10 @@
         <v>53</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -4337,10 +4425,10 @@
         <v>53</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>218</v>
+        <v>299</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -4348,10 +4436,10 @@
         <v>53</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -4359,10 +4447,10 @@
         <v>53</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -4370,10 +4458,10 @@
         <v>53</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>221</v>
+        <v>265</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -4381,10 +4469,10 @@
         <v>53</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -4392,10 +4480,10 @@
         <v>53</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -4403,10 +4491,10 @@
         <v>53</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -4414,10 +4502,10 @@
         <v>53</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -4425,10 +4513,10 @@
         <v>53</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>198</v>
+        <v>285</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -4436,10 +4524,10 @@
         <v>53</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -4447,10 +4535,10 @@
         <v>53</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -4458,10 +4546,10 @@
         <v>53</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -4469,10 +4557,10 @@
         <v>53</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -4480,10 +4568,10 @@
         <v>53</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>269</v>
+        <v>220</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -4491,10 +4579,10 @@
         <v>53</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>268</v>
+        <v>221</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -4502,10 +4590,10 @@
         <v>53</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -4513,10 +4601,10 @@
         <v>53</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -4524,10 +4612,10 @@
         <v>53</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -4535,10 +4623,10 @@
         <v>53</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -4546,10 +4634,10 @@
         <v>53</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -4557,10 +4645,10 @@
         <v>53</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -4568,10 +4656,10 @@
         <v>53</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>438</v>
+        <v>200</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>439</v>
+        <v>487</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -4579,10 +4667,10 @@
         <v>53</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -4590,10 +4678,10 @@
         <v>53</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>70</v>
+        <v>479</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -4601,10 +4689,10 @@
         <v>53</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>70</v>
+        <v>231</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>69</v>
+        <v>231</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -4612,10 +4700,10 @@
         <v>53</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -4623,10 +4711,10 @@
         <v>53</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -4634,10 +4722,10 @@
         <v>53</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -4645,10 +4733,10 @@
         <v>53</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -4656,10 +4744,10 @@
         <v>53</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>236</v>
+        <v>276</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -4667,10 +4755,10 @@
         <v>53</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -4678,10 +4766,10 @@
         <v>53</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>77</v>
+        <v>274</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -4689,10 +4777,10 @@
         <v>53</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>76</v>
+        <v>191</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -4700,10 +4788,10 @@
         <v>53</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -4711,10 +4799,10 @@
         <v>53</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>203</v>
+        <v>438</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>201</v>
+        <v>439</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -4722,10 +4810,10 @@
         <v>53</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>203</v>
+        <v>438</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>203</v>
+        <v>438</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -4733,10 +4821,10 @@
         <v>53</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>203</v>
+        <v>70</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>202</v>
+        <v>70</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -4744,10 +4832,10 @@
         <v>53</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>245</v>
+        <v>70</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>245</v>
+        <v>69</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -4755,10 +4843,10 @@
         <v>53</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -4766,10 +4854,10 @@
         <v>53</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -4777,10 +4865,10 @@
         <v>53</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -4788,10 +4876,10 @@
         <v>53</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -4799,10 +4887,10 @@
         <v>53</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>206</v>
+        <v>491</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -4810,10 +4898,10 @@
         <v>53</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -4821,10 +4909,10 @@
         <v>53</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>246</v>
+        <v>492</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -4832,10 +4920,10 @@
         <v>53</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -4843,10 +4931,10 @@
         <v>53</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -4854,10 +4942,10 @@
         <v>53</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -4865,10 +4953,10 @@
         <v>53</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>208</v>
+        <v>241</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -4876,10 +4964,10 @@
         <v>53</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -4887,10 +4975,10 @@
         <v>53</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -4898,10 +4986,10 @@
         <v>53</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>217</v>
+        <v>488</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -4909,10 +4997,10 @@
         <v>53</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>217</v>
+        <v>481</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>215</v>
+        <v>481</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -4920,10 +5008,10 @@
         <v>53</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>252</v>
+        <v>481</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>252</v>
+        <v>201</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -4931,10 +5019,10 @@
         <v>53</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -4942,10 +5030,10 @@
         <v>53</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -4953,10 +5041,10 @@
         <v>53</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -4964,10 +5052,10 @@
         <v>53</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -4975,10 +5063,10 @@
         <v>53</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>257</v>
+        <v>206</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -4986,10 +5074,10 @@
         <v>53</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>256</v>
+        <v>489</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -4997,10 +5085,10 @@
         <v>53</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>255</v>
+        <v>205</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -5008,10 +5096,10 @@
         <v>53</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>259</v>
+        <v>483</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>259</v>
+        <v>483</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -5019,10 +5107,10 @@
         <v>53</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>259</v>
+        <v>483</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>258</v>
+        <v>204</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -5030,10 +5118,10 @@
         <v>53</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -5041,10 +5129,10 @@
         <v>53</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -5052,10 +5140,10 @@
         <v>53</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>263</v>
+        <v>209</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -5063,10 +5151,10 @@
         <v>53</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>261</v>
+        <v>490</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -5074,10 +5162,10 @@
         <v>53</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -5085,10 +5173,10 @@
         <v>53</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>271</v>
+        <v>485</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>270</v>
+        <v>485</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -5096,10 +5184,10 @@
         <v>53</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>271</v>
+        <v>485</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>271</v>
+        <v>207</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -5107,10 +5195,10 @@
         <v>53</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -5118,10 +5206,10 @@
         <v>53</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>273</v>
+        <v>217</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -5129,10 +5217,10 @@
         <v>53</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>51</v>
+        <v>217</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -5140,10 +5228,10 @@
         <v>53</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>51</v>
+        <v>217</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>52</v>
+        <v>215</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -5151,10 +5239,10 @@
         <v>53</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>51</v>
+        <v>252</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>51</v>
+        <v>252</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -5162,10 +5250,10 @@
         <v>53</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -5173,10 +5261,10 @@
         <v>53</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -5184,10 +5272,10 @@
         <v>53</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>284</v>
+        <v>253</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -5195,10 +5283,10 @@
         <v>53</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -5206,1641 +5294,1641 @@
         <v>53</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
       <c r="A290" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
       <c r="A291" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
       <c r="A292" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
       <c r="A293" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
       <c r="A294" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
       <c r="A295" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
       <c r="A296" s="1" t="s">
-        <v>464</v>
+        <v>53</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>468</v>
+        <v>262</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
-        <v>464</v>
+        <v>53</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>466</v>
+        <v>262</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
       <c r="A298" s="1" t="s">
-        <v>464</v>
+        <v>53</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>470</v>
+        <v>75</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
       <c r="A299" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>442</v>
+        <v>271</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
       <c r="A300" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
       <c r="A301" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>441</v>
+        <v>273</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
       <c r="A302" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>441</v>
+        <v>273</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D302" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
       <c r="A303" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>441</v>
+        <v>51</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
       <c r="A304" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>307</v>
+        <v>51</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>445</v>
+        <v>52</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>307</v>
+        <v>51</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>307</v>
+        <v>51</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>448</v>
+        <v>283</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>447</v>
+        <v>283</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" s="1" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>448</v>
+        <v>283</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>448</v>
+        <v>284</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>306</v>
+        <v>494</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>440</v>
+        <v>289</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>440</v>
+        <v>289</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>440</v>
+        <v>289</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>444</v>
+        <v>287</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>440</v>
+        <v>292</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>443</v>
+        <v>290</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>447</v>
+        <v>295</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>447</v>
+        <v>294</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" s="1" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>447</v>
+        <v>295</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>448</v>
+        <v>295</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" s="1" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" s="1" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C320" s="4" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3">
+        <v>470</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
       <c r="A321" s="1" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
       <c r="A322" s="1" t="s">
-        <v>449</v>
+        <v>302</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C322" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3">
-      <c r="A323" s="2" t="s">
-        <v>417</v>
+        <v>442</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>418</v>
+        <v>304</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3">
-      <c r="A324" s="2" t="s">
-        <v>417</v>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3">
-      <c r="A325" s="2" t="s">
-        <v>417</v>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3">
-      <c r="A326" s="2" t="s">
-        <v>417</v>
+        <v>444</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3">
-      <c r="A327" s="2" t="s">
-        <v>417</v>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3">
-      <c r="A328" s="2" t="s">
-        <v>417</v>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>431</v>
+        <v>307</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3">
-      <c r="A329" s="2" t="s">
-        <v>417</v>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>421</v>
+        <v>307</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3">
-      <c r="A330" s="2" t="s">
-        <v>417</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3">
-      <c r="A331" s="2" t="s">
-        <v>417</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3">
-      <c r="A332" s="2" t="s">
-        <v>417</v>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>429</v>
+        <v>306</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
       <c r="A333" s="1" t="s">
-        <v>92</v>
+        <v>305</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>94</v>
+        <v>306</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
       <c r="A334" s="1" t="s">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
       <c r="A335" s="1" t="s">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
       <c r="A336" s="1" t="s">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>95</v>
+        <v>443</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" s="1" t="s">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>84</v>
+        <v>308</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>85</v>
+        <v>307</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" s="1" t="s">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" s="1" t="s">
-        <v>87</v>
+        <v>305</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>88</v>
+        <v>447</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>95</v>
+        <v>447</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" s="1" t="s">
-        <v>87</v>
+        <v>305</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>88</v>
+        <v>447</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>88</v>
+        <v>448</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" s="1" t="s">
-        <v>87</v>
+        <v>449</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>88</v>
+        <v>450</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>97</v>
+        <v>450</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" s="1" t="s">
-        <v>87</v>
+        <v>449</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C343" s="1" t="s">
-        <v>90</v>
+        <v>450</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" s="1" t="s">
-        <v>87</v>
+        <v>449</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>89</v>
+        <v>452</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>96</v>
+        <v>452</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" s="1" t="s">
-        <v>87</v>
+        <v>449</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>98</v>
+        <v>452</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="346" spans="1:3">
-      <c r="A346" s="1" t="s">
-        <v>87</v>
+      <c r="A346" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>89</v>
+        <v>418</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>89</v>
+        <v>423</v>
       </c>
     </row>
     <row r="347" spans="1:3">
-      <c r="A347" s="1" t="s">
-        <v>87</v>
+      <c r="A347" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>89</v>
+        <v>419</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>91</v>
+        <v>435</v>
       </c>
     </row>
     <row r="348" spans="1:3">
-      <c r="A348" s="1" t="s">
-        <v>117</v>
+      <c r="A348" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>118</v>
+        <v>420</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>127</v>
+        <v>432</v>
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="1" t="s">
-        <v>117</v>
+      <c r="A349" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>119</v>
+        <v>434</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="1" t="s">
-        <v>117</v>
+      <c r="A350" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>119</v>
+        <v>436</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>125</v>
+        <v>437</v>
       </c>
     </row>
     <row r="351" spans="1:3">
-      <c r="A351" s="1" t="s">
-        <v>117</v>
+      <c r="A351" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>119</v>
+        <v>431</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>128</v>
+        <v>426</v>
       </c>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="1" t="s">
-        <v>117</v>
+      <c r="A352" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>121</v>
+        <v>421</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="1" t="s">
-        <v>117</v>
+      <c r="A353" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>121</v>
+        <v>430</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>123</v>
+        <v>425</v>
       </c>
     </row>
     <row r="354" spans="1:3">
-      <c r="A354" s="1" t="s">
-        <v>117</v>
+      <c r="A354" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>121</v>
+        <v>422</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>130</v>
+        <v>433</v>
       </c>
     </row>
     <row r="355" spans="1:3">
-      <c r="A355" s="1" t="s">
-        <v>117</v>
+      <c r="A355" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>120</v>
+        <v>429</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>460</v>
+        <v>424</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" s="1" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>461</v>
+        <v>96</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" s="1" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>24</v>
+        <v>458</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>314</v>
+        <v>119</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>311</v>
+        <v>128</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>314</v>
+        <v>121</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>312</v>
+        <v>459</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>314</v>
+        <v>121</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>313</v>
+        <v>123</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>317</v>
+        <v>121</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>318</v>
+        <v>130</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>319</v>
+        <v>120</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>320</v>
+        <v>460</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>321</v>
+        <v>120</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>322</v>
+        <v>124</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>327</v>
+        <v>120</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>328</v>
+        <v>129</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>325</v>
+        <v>122</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>326</v>
+        <v>461</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>329</v>
+        <v>122</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>330</v>
+        <v>126</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>331</v>
+        <v>122</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>332</v>
+        <v>131</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>331</v>
+        <v>8</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>333</v>
+        <v>23</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>331</v>
+        <v>8</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>334</v>
+        <v>40</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>335</v>
+        <v>8</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>337</v>
+        <v>26</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>338</v>
+        <v>35</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>323</v>
+        <v>27</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>324</v>
+        <v>36</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>339</v>
+        <v>28</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>340</v>
+        <v>37</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>341</v>
+        <v>29</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>342</v>
+        <v>38</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>315</v>
+        <v>30</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>316</v>
+        <v>31</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>315</v>
+        <v>32</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>343</v>
+        <v>33</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>344</v>
+        <v>8</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>345</v>
+        <v>24</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" s="1" t="s">
-        <v>454</v>
+        <v>48</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>455</v>
+        <v>34</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>455</v>
+        <v>39</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" s="1" t="s">
-        <v>456</v>
+        <v>310</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>457</v>
+        <v>314</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>455</v>
+        <v>311</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" s="1" t="s">
-        <v>456</v>
+        <v>310</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>457</v>
+        <v>314</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>457</v>
+        <v>312</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>19</v>
+        <v>313</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>20</v>
+        <v>317</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>21</v>
+        <v>318</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>23</v>
+        <v>320</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>22</v>
+        <v>321</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>25</v>
+        <v>322</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>22</v>
+        <v>327</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>24</v>
+        <v>328</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>99</v>
+        <v>325</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>104</v>
+        <v>326</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>105</v>
+        <v>329</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>106</v>
+        <v>330</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>100</v>
+        <v>331</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>101</v>
+        <v>332</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>100</v>
+        <v>331</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>103</v>
+        <v>333</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>8</v>
+        <v>331</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>23</v>
+        <v>334</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>8</v>
+        <v>335</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>40</v>
+        <v>336</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>8</v>
+        <v>337</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>24</v>
+        <v>338</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>462</v>
+        <v>324</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>8</v>
+        <v>339</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>472</v>
+        <v>340</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>471</v>
+        <v>342</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" s="1" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>360</v>
+        <v>316</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" s="1" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" s="1" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>382</v>
+        <v>8</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>380</v>
+        <v>25</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" s="1" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>387</v>
+        <v>8</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>387</v>
+        <v>24</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" s="1" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
-        <v>346</v>
+        <v>454</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>354</v>
+        <v>455</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>353</v>
+        <v>455</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" s="1" t="s">
-        <v>346</v>
+        <v>456</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>384</v>
+        <v>457</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>384</v>
+        <v>455</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" s="1" t="s">
-        <v>346</v>
+        <v>456</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>357</v>
+        <v>457</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>358</v>
+        <v>457</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>357</v>
+        <v>18</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>356</v>
+        <v>19</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>364</v>
+        <v>20</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>364</v>
+        <v>21</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>364</v>
+        <v>22</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>365</v>
+        <v>23</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>364</v>
+        <v>22</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>366</v>
+        <v>25</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>348</v>
+        <v>22</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>348</v>
+        <v>24</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>359</v>
+        <v>99</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>359</v>
+        <v>104</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>383</v>
+        <v>105</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>383</v>
+        <v>106</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" s="1" t="s">
-        <v>346</v>
+        <v>473</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>385</v>
+        <v>100</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>385</v>
+        <v>101</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>349</v>
+        <v>100</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>349</v>
+        <v>103</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>349</v>
+        <v>8</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>369</v>
+        <v>462</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>370</v>
+        <v>8</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>370</v>
+        <v>471</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>370</v>
+        <v>8</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>372</v>
+        <v>472</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>370</v>
+        <v>8</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>371</v>
+        <v>23</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>374</v>
+        <v>8</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>375</v>
+        <v>40</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>374</v>
+        <v>8</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>373</v>
+        <v>24</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -6848,10 +6936,10 @@
         <v>346</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -6859,10 +6947,10 @@
         <v>346</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>386</v>
+        <v>347</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -6870,10 +6958,10 @@
         <v>346</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -6881,10 +6969,10 @@
         <v>346</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -6892,10 +6980,10 @@
         <v>346</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -6903,10 +6991,10 @@
         <v>346</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -6914,10 +7002,10 @@
         <v>346</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -6925,10 +7013,10 @@
         <v>346</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -6936,10 +7024,10 @@
         <v>346</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -6947,59 +7035,59 @@
         <v>346</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>392</v>
+        <v>348</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>383</v>
@@ -7010,302 +7098,555 @@
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>394</v>
+        <v>349</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>403</v>
+        <v>370</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>409</v>
+        <v>363</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>394</v>
+        <v>361</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>411</v>
+        <v>350</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>411</v>
+        <v>367</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>411</v>
+        <v>350</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>396</v>
+        <v>368</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>398</v>
+        <v>350</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>412</v>
+        <v>351</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>412</v>
+        <v>351</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>412</v>
+        <v>378</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" s="1" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>414</v>
+        <v>380</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" s="1" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" s="1" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" s="1" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" s="1" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" s="1" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3">
+      <c r="A478" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C478" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3">
+      <c r="A479" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3">
+      <c r="A480" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3">
+      <c r="A481" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3">
+      <c r="A482" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3">
+      <c r="A483" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3">
+      <c r="A485" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C485" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3">
+      <c r="A486" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B477" s="1" t="s">
+      <c r="B486" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C486" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3">
+      <c r="A487" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C487" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3">
+      <c r="A488" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C488" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3">
+      <c r="A489" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C489" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3">
+      <c r="A490" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3">
+      <c r="A491" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C491" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3">
+      <c r="A492" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C492" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3">
+      <c r="A493" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C493" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3">
+      <c r="A494" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C494" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3">
+      <c r="A495" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C495" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3">
+      <c r="A496" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C496" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3">
+      <c r="A497" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C497" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3">
+      <c r="A498" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C498" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3">
+      <c r="A499" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C499" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3">
+      <c r="A500" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B500" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C477" s="1" t="s">
+      <c r="C500" s="1" t="s">
         <v>401</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C409" xr:uid="{799D48F5-B989-4AA3-BCE2-AE0AB96B6C6B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C409">
-      <sortCondition ref="A2:A409"/>
-      <sortCondition ref="B2:B409"/>
-      <sortCondition ref="C2:C409"/>
+  <autoFilter ref="A1:C500" xr:uid="{799D48F5-B989-4AA3-BCE2-AE0AB96B6C6B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C432">
+      <sortCondition ref="A2:A432"/>
+      <sortCondition ref="B2:B432"/>
+      <sortCondition ref="C2:C432"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D477">
-    <sortCondition ref="A2:A477"/>
-    <sortCondition ref="B2:B477"/>
-    <sortCondition ref="C2:C477"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D500">
+    <sortCondition ref="A2:A500"/>
+    <sortCondition ref="B2:B500"/>
+    <sortCondition ref="C2:C500"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/CT Term Mapping Dictionary.xlsx
+++ b/config/CT Term Mapping Dictionary.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shirley.ho\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B8E33B-BA45-4A09-8B9A-DE8E7488E63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAD7697-A352-4DB8-9D78-6BA38ED87AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51DA8FFF-F53B-43BA-9BD3-FE23D4CF3F85}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51DA8FFF-F53B-43BA-9BD3-FE23D4CF3F85}"/>
   </bookViews>
   <sheets>
     <sheet name="CT Term Mapping" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CT Term Mapping'!$A$1:$C$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CT Term Mapping'!$A$1:$C$539</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="552">
   <si>
     <t>CTVAL</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1694,6 +1694,220 @@
   </si>
   <si>
     <t>WHITE BLOOD CELLS (WBC)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dispensed Amount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AURICULAR (OTIC)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CT SCAN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MRI</t>
+  </si>
+  <si>
+    <t>mm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OROPHARYNGEAL</t>
+  </si>
+  <si>
+    <t>GAR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>INTRATHECAL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRANSDERMAL</t>
+  </si>
+  <si>
+    <t>TD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADRENAL GLAND</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adrenal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLADDER</t>
+  </si>
+  <si>
+    <t>Bladder</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BONE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRAIN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BREAST</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Colorectal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COLON</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kidney</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KIDNEY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Liver</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIVER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lung</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LUNG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lymph Nodes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LYMPH NODE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lymph Node</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ovary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OVARY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pancreas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PANCREAS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skin/ Soft Tissue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKIN</t>
+  </si>
+  <si>
+    <t>TRTEST</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRTESTCD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIAMETER</t>
+  </si>
+  <si>
+    <t>DIAMETER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diameter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUMDIAM</t>
+  </si>
+  <si>
+    <t>Sum of Diameter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tumor State</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TUMSTATE</t>
+  </si>
+  <si>
+    <t>TUTEST</t>
+  </si>
+  <si>
+    <t>TUTESTCD</t>
+  </si>
+  <si>
+    <t>NTIND</t>
+  </si>
+  <si>
+    <t>Non-Target Indicator</t>
+  </si>
+  <si>
+    <t>Non-Target Indicator</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIND</t>
+  </si>
+  <si>
+    <t>Target Indicator</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TUMIDENT</t>
+  </si>
+  <si>
+    <t>Tumor Identification</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2120,7 +2334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799D48F5-B989-4AA3-BCE2-AE0AB96B6C6B}">
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:D539"/>
   <sheetFormatPr defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -2335,7 +2549,7 @@
         <v>137</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>138</v>
+        <v>495</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>138</v>
@@ -5635,10 +5849,10 @@
         <v>464</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -5646,1036 +5860,1036 @@
         <v>464</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
         <v>464</v>
       </c>
       <c r="B321" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C321" s="1" t="s">
+      <c r="C335" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="322" spans="1:4">
-      <c r="A322" s="1" t="s">
+    <row r="336" spans="1:3">
+      <c r="A336" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="B336" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C322" s="1" t="s">
+      <c r="C336" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="323" spans="1:4">
-      <c r="A323" s="1" t="s">
+    <row r="337" spans="1:4">
+      <c r="A337" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B323" s="1" t="s">
+      <c r="B337" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C323" s="1" t="s">
+      <c r="C337" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="324" spans="1:4">
-      <c r="A324" s="1" t="s">
+    <row r="338" spans="1:4">
+      <c r="A338" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B324" s="1" t="s">
+      <c r="B338" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C324" s="1" t="s">
+      <c r="C338" s="1" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="325" spans="1:4">
-      <c r="A325" s="1" t="s">
+    <row r="339" spans="1:4">
+      <c r="A339" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B325" s="1" t="s">
+      <c r="B339" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C325" s="1" t="s">
+      <c r="C339" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D325" s="3" t="s">
+      <c r="D339" s="3" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="326" spans="1:4">
-      <c r="A326" s="1" t="s">
+    <row r="340" spans="1:4">
+      <c r="A340" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B326" s="1" t="s">
+      <c r="B340" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C326" s="1" t="s">
+      <c r="C340" s="1" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="327" spans="1:4">
-      <c r="A327" s="1" t="s">
+    <row r="341" spans="1:4">
+      <c r="A341" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B327" s="1" t="s">
+      <c r="B341" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C327" s="1" t="s">
+      <c r="C341" s="1" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="328" spans="1:4">
-      <c r="A328" s="1" t="s">
+    <row r="342" spans="1:4">
+      <c r="A342" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="B342" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C328" s="1" t="s">
+      <c r="C342" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="329" spans="1:4">
-      <c r="A329" s="1" t="s">
+    <row r="343" spans="1:4">
+      <c r="A343" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B329" s="1" t="s">
+      <c r="B343" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C329" s="1" t="s">
+      <c r="C343" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="330" spans="1:4">
-      <c r="A330" s="1" t="s">
+    <row r="344" spans="1:4">
+      <c r="A344" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B330" s="1" t="s">
+      <c r="B344" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C330" s="1" t="s">
+      <c r="C344" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="331" spans="1:4">
-      <c r="A331" s="1" t="s">
+    <row r="345" spans="1:4">
+      <c r="A345" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B331" s="1" t="s">
+      <c r="B345" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C331" s="1" t="s">
+      <c r="C345" s="1" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="332" spans="1:4">
-      <c r="A332" s="1" t="s">
+    <row r="346" spans="1:4">
+      <c r="A346" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B332" s="1" t="s">
+      <c r="B346" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C332" s="1" t="s">
+      <c r="C346" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="333" spans="1:4">
-      <c r="A333" s="1" t="s">
+    <row r="347" spans="1:4">
+      <c r="A347" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B333" s="1" t="s">
+      <c r="B347" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C333" s="1" t="s">
+      <c r="C347" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="334" spans="1:4">
-      <c r="A334" s="1" t="s">
+    <row r="348" spans="1:4">
+      <c r="A348" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B334" s="1" t="s">
+      <c r="B348" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C334" s="1" t="s">
+      <c r="C348" s="1" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="335" spans="1:4">
-      <c r="A335" s="1" t="s">
+    <row r="349" spans="1:4">
+      <c r="A349" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B335" s="1" t="s">
+      <c r="B349" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C335" s="1" t="s">
+      <c r="C349" s="1" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="336" spans="1:4">
-      <c r="A336" s="1" t="s">
+    <row r="350" spans="1:4">
+      <c r="A350" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B336" s="1" t="s">
+      <c r="B350" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C336" s="1" t="s">
+      <c r="C350" s="1" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
-      <c r="A337" s="1" t="s">
+    <row r="351" spans="1:4">
+      <c r="A351" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B337" s="1" t="s">
+      <c r="B351" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C337" s="1" t="s">
+      <c r="C351" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="338" spans="1:3">
-      <c r="A338" s="1" t="s">
+    <row r="352" spans="1:4">
+      <c r="A352" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="B352" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C338" s="1" t="s">
+      <c r="C352" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
-      <c r="A339" s="1" t="s">
+    <row r="353" spans="1:3">
+      <c r="A353" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="B353" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C339" s="1" t="s">
+      <c r="C353" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
-      <c r="A340" s="1" t="s">
+    <row r="354" spans="1:3">
+      <c r="A354" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B340" s="1" t="s">
+      <c r="B354" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C340" s="1" t="s">
+      <c r="C354" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
-      <c r="A341" s="1" t="s">
+    <row r="355" spans="1:3">
+      <c r="A355" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B341" s="1" t="s">
+      <c r="B355" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C341" s="1" t="s">
+      <c r="C355" s="1" t="s">
         <v>448</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3">
-      <c r="A342" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B342" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3">
-      <c r="A343" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B343" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C343" s="4" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3">
-      <c r="A344" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B344" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3">
-      <c r="A345" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B345" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C345" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3">
-      <c r="A346" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B346" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3">
-      <c r="A347" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B347" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3">
-      <c r="A348" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B348" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3">
-      <c r="A349" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B349" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3">
-      <c r="A350" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B350" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3">
-      <c r="A351" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3">
-      <c r="A352" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3">
-      <c r="A353" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3">
-      <c r="A354" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3">
-      <c r="A355" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B355" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" s="1" t="s">
-        <v>92</v>
+        <v>449</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>94</v>
+        <v>498</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>93</v>
+        <v>498</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" s="1" t="s">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>83</v>
+        <v>497</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" s="1" t="s">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>78</v>
+        <v>499</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>96</v>
+        <v>499</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" s="1" t="s">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>95</v>
+        <v>450</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" s="1" t="s">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C360" s="1" t="s">
-        <v>84</v>
+        <v>450</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" s="1" t="s">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>80</v>
+        <v>452</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>85</v>
+        <v>452</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C362" s="1" t="s">
-        <v>86</v>
+        <v>452</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="363" spans="1:3">
-      <c r="A363" s="1" t="s">
-        <v>87</v>
+      <c r="A363" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>88</v>
+        <v>418</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>95</v>
+        <v>423</v>
       </c>
     </row>
     <row r="364" spans="1:3">
-      <c r="A364" s="1" t="s">
-        <v>87</v>
+      <c r="A364" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>88</v>
+        <v>419</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>88</v>
+        <v>435</v>
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="1" t="s">
-        <v>87</v>
+      <c r="A365" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>88</v>
+        <v>420</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>97</v>
+        <v>432</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="1" t="s">
-        <v>87</v>
+      <c r="A366" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>88</v>
+        <v>434</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>90</v>
+        <v>427</v>
       </c>
     </row>
     <row r="367" spans="1:3">
-      <c r="A367" s="1" t="s">
-        <v>87</v>
+      <c r="A367" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>89</v>
+        <v>436</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>96</v>
+        <v>437</v>
       </c>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="1" t="s">
-        <v>87</v>
+      <c r="A368" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>89</v>
+        <v>431</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>98</v>
+        <v>426</v>
       </c>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="1" t="s">
-        <v>87</v>
+      <c r="A369" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>89</v>
+        <v>421</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>89</v>
+        <v>428</v>
       </c>
     </row>
     <row r="370" spans="1:3">
-      <c r="A370" s="1" t="s">
-        <v>87</v>
+      <c r="A370" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>89</v>
+        <v>430</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>91</v>
+        <v>425</v>
       </c>
     </row>
     <row r="371" spans="1:3">
-      <c r="A371" s="1" t="s">
-        <v>117</v>
+      <c r="A371" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>118</v>
+        <v>422</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>127</v>
+        <v>433</v>
       </c>
     </row>
     <row r="372" spans="1:3">
-      <c r="A372" s="1" t="s">
-        <v>117</v>
+      <c r="A372" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>119</v>
+        <v>429</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>458</v>
+        <v>424</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" s="1" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>459</v>
+        <v>96</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>460</v>
+        <v>85</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" s="1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" s="1" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" s="1" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>461</v>
+        <v>88</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" s="1" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" s="1" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" s="1" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" s="1" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>37</v>
+        <v>458</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>33</v>
+        <v>459</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>24</v>
+        <v>460</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>311</v>
+        <v>129</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>314</v>
+        <v>122</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>312</v>
+        <v>461</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>314</v>
+        <v>122</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>313</v>
+        <v>126</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>317</v>
+        <v>122</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>318</v>
+        <v>131</v>
       </c>
     </row>
     <row r="401" spans="1:3">
       <c r="A401" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>319</v>
+        <v>8</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>320</v>
+        <v>23</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>321</v>
+        <v>8</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>322</v>
+        <v>40</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
-        <v>310</v>
+        <v>117</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>327</v>
+        <v>8</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>328</v>
+        <v>24</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>325</v>
+        <v>26</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>326</v>
+        <v>35</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>329</v>
+        <v>27</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>330</v>
+        <v>36</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>332</v>
+        <v>37</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>331</v>
+        <v>29</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>333</v>
+        <v>38</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>331</v>
+        <v>30</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>334</v>
+        <v>31</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>335</v>
+        <v>32</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>336</v>
+        <v>33</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>337</v>
+        <v>8</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>338</v>
+        <v>23</v>
       </c>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>324</v>
+        <v>40</v>
       </c>
     </row>
     <row r="412" spans="1:3">
       <c r="A412" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>339</v>
+        <v>8</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>340</v>
+        <v>24</v>
       </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>341</v>
+        <v>34</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>342</v>
+        <v>39</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -6683,10 +6897,10 @@
         <v>310</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -6694,10 +6908,10 @@
         <v>310</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>315</v>
+        <v>496</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -6705,10 +6919,10 @@
         <v>310</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>8</v>
+        <v>314</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>25</v>
+        <v>313</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -6716,10 +6930,10 @@
         <v>310</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>8</v>
+        <v>317</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>24</v>
+        <v>318</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -6727,926 +6941,1355 @@
         <v>310</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
-        <v>454</v>
+        <v>310</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>455</v>
+        <v>321</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>455</v>
+        <v>322</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" s="1" t="s">
-        <v>456</v>
+        <v>310</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>457</v>
+        <v>503</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>455</v>
+        <v>504</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" s="1" t="s">
-        <v>456</v>
+        <v>310</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>457</v>
+        <v>327</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>457</v>
+        <v>328</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>18</v>
+        <v>325</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>19</v>
+        <v>326</v>
       </c>
     </row>
     <row r="423" spans="1:3">
       <c r="A423" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>21</v>
+        <v>330</v>
       </c>
     </row>
     <row r="424" spans="1:3">
       <c r="A424" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>22</v>
+        <v>331</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>23</v>
+        <v>332</v>
       </c>
     </row>
     <row r="425" spans="1:3">
       <c r="A425" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>22</v>
+        <v>331</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>25</v>
+        <v>333</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" s="1" t="s">
-        <v>47</v>
+        <v>310</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>22</v>
+        <v>331</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>24</v>
+        <v>334</v>
       </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>99</v>
+        <v>335</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>104</v>
+        <v>336</v>
       </c>
     </row>
     <row r="428" spans="1:3">
       <c r="A428" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>105</v>
+        <v>501</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>106</v>
+        <v>501</v>
       </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429" s="1" t="s">
-        <v>473</v>
+        <v>310</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>100</v>
+        <v>501</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>101</v>
+        <v>502</v>
       </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>100</v>
+        <v>337</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>103</v>
+        <v>338</v>
       </c>
     </row>
     <row r="431" spans="1:3">
       <c r="A431" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>462</v>
+        <v>324</v>
       </c>
     </row>
     <row r="432" spans="1:3">
       <c r="A432" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>8</v>
+        <v>339</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>471</v>
+        <v>340</v>
       </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>472</v>
+        <v>342</v>
       </c>
     </row>
     <row r="434" spans="1:3">
       <c r="A434" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>8</v>
+        <v>315</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>23</v>
+        <v>316</v>
       </c>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>8</v>
+        <v>315</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>40</v>
+        <v>343</v>
       </c>
     </row>
     <row r="436" spans="1:3">
       <c r="A436" s="1" t="s">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>8</v>
+        <v>505</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>24</v>
+        <v>506</v>
       </c>
     </row>
     <row r="437" spans="1:3">
       <c r="A437" s="1" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>360</v>
+        <v>8</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>360</v>
+        <v>25</v>
       </c>
     </row>
     <row r="438" spans="1:3">
       <c r="A438" s="1" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>352</v>
+        <v>8</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>347</v>
+        <v>24</v>
       </c>
     </row>
     <row r="439" spans="1:3">
       <c r="A439" s="1" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>382</v>
+        <v>344</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>380</v>
+        <v>345</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
-        <v>346</v>
+        <v>454</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>387</v>
+        <v>455</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>387</v>
+        <v>455</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" s="1" t="s">
-        <v>346</v>
+        <v>456</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>354</v>
+        <v>457</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>355</v>
+        <v>455</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" s="1" t="s">
-        <v>346</v>
+        <v>456</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>354</v>
+        <v>457</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>353</v>
+        <v>457</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>384</v>
+        <v>18</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>384</v>
+        <v>19</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>358</v>
+        <v>21</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>357</v>
+        <v>22</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>356</v>
+        <v>23</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>364</v>
+        <v>22</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>364</v>
+        <v>25</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" s="1" t="s">
-        <v>346</v>
+        <v>47</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>364</v>
+        <v>22</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>364</v>
+        <v>99</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>366</v>
+        <v>104</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>348</v>
+        <v>105</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>348</v>
+        <v>106</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" s="1" t="s">
-        <v>346</v>
+        <v>473</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>359</v>
+        <v>100</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>359</v>
+        <v>101</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>383</v>
+        <v>100</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>383</v>
+        <v>103</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>385</v>
+        <v>8</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>385</v>
+        <v>462</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>349</v>
+        <v>8</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>349</v>
+        <v>471</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>349</v>
+        <v>8</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>369</v>
+        <v>472</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>370</v>
+        <v>8</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>370</v>
+        <v>23</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>370</v>
+        <v>8</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>372</v>
+        <v>40</v>
       </c>
     </row>
     <row r="457" spans="1:3">
       <c r="A457" s="1" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>370</v>
+        <v>8</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>371</v>
+        <v>24</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" s="1" t="s">
-        <v>346</v>
+        <v>534</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>374</v>
+        <v>538</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>375</v>
+        <v>538</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" s="1" t="s">
-        <v>346</v>
+        <v>534</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>374</v>
+        <v>540</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>373</v>
+        <v>540</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
-        <v>346</v>
+        <v>534</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>377</v>
+        <v>541</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>376</v>
+        <v>541</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" s="1" t="s">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>386</v>
+        <v>537</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>386</v>
+        <v>536</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" s="1" t="s">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>381</v>
+        <v>539</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>381</v>
+        <v>539</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" s="1" t="s">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>362</v>
+        <v>539</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>363</v>
+        <v>540</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" s="1" t="s">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>362</v>
+        <v>542</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>361</v>
+        <v>542</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" s="1" t="s">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>350</v>
+        <v>542</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>367</v>
+        <v>541</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" s="1" t="s">
-        <v>346</v>
+        <v>543</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>350</v>
+        <v>546</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>368</v>
+        <v>547</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" s="1" t="s">
-        <v>346</v>
+        <v>543</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>350</v>
+        <v>549</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>350</v>
+        <v>549</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
-        <v>346</v>
+        <v>543</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>351</v>
+        <v>551</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>379</v>
+        <v>551</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" s="1" t="s">
-        <v>346</v>
+        <v>544</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>351</v>
+        <v>545</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>378</v>
+        <v>545</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" s="1" t="s">
-        <v>388</v>
+        <v>544</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>380</v>
+        <v>545</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>380</v>
+        <v>546</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" s="1" t="s">
-        <v>388</v>
+        <v>544</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>389</v>
+        <v>548</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>389</v>
+        <v>548</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" s="1" t="s">
-        <v>388</v>
+        <v>544</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>392</v>
+        <v>548</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>392</v>
+        <v>549</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" s="1" t="s">
-        <v>388</v>
+        <v>544</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>390</v>
+        <v>550</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>390</v>
+        <v>550</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" s="1" t="s">
-        <v>388</v>
+        <v>544</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>383</v>
+        <v>550</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>383</v>
+        <v>551</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>393</v>
+        <v>352</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>393</v>
+        <v>347</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>397</v>
+        <v>354</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>404</v>
+        <v>355</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>400</v>
+        <v>357</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>407</v>
+        <v>358</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="A483" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>406</v>
+        <v>357</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>395</v>
+        <v>356</v>
       </c>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>406</v>
+        <v>364</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>406</v>
+        <v>364</v>
       </c>
     </row>
     <row r="485" spans="1:3">
       <c r="A485" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>401</v>
+        <v>365</v>
       </c>
     </row>
     <row r="486" spans="1:3">
       <c r="A486" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>409</v>
+        <v>364</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>409</v>
+        <v>366</v>
       </c>
     </row>
     <row r="487" spans="1:3">
       <c r="A487" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>409</v>
+        <v>348</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>394</v>
+        <v>348</v>
       </c>
     </row>
     <row r="488" spans="1:3">
       <c r="A488" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>411</v>
+        <v>359</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>411</v>
+        <v>359</v>
       </c>
     </row>
     <row r="489" spans="1:3">
       <c r="A489" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="A490" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
     </row>
     <row r="491" spans="1:3">
       <c r="A491" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>412</v>
+        <v>349</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>404</v>
+        <v>349</v>
       </c>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>412</v>
+        <v>349</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>412</v>
+        <v>369</v>
       </c>
     </row>
     <row r="493" spans="1:3">
       <c r="A493" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>414</v>
+        <v>370</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>414</v>
+        <v>370</v>
       </c>
     </row>
     <row r="494" spans="1:3">
       <c r="A494" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>414</v>
+        <v>370</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>405</v>
+        <v>372</v>
       </c>
     </row>
     <row r="495" spans="1:3">
       <c r="A495" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>415</v>
+        <v>371</v>
       </c>
     </row>
     <row r="496" spans="1:3">
       <c r="A496" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>415</v>
+        <v>374</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>407</v>
+        <v>375</v>
       </c>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
     </row>
     <row r="498" spans="1:3">
       <c r="A498" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
     </row>
     <row r="499" spans="1:3">
       <c r="A499" s="1" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>406</v>
+        <v>500</v>
       </c>
     </row>
     <row r="500" spans="1:3">
       <c r="A500" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C500" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3">
+      <c r="A501" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C501" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3">
+      <c r="A502" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C502" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3">
+      <c r="A503" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C503" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3">
+      <c r="A504" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C504" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3">
+      <c r="A505" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3">
+      <c r="A506" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C506" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3">
+      <c r="A507" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3">
+      <c r="A508" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C508" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3">
+      <c r="A509" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3">
+      <c r="A510" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C510" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3">
+      <c r="A511" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C511" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3">
+      <c r="A512" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C512" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3">
+      <c r="A513" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3">
+      <c r="A514" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3">
+      <c r="A515" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C515" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3">
+      <c r="A516" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C516" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3">
+      <c r="A517" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3">
+      <c r="A518" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C518" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3">
+      <c r="A519" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C519" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3">
+      <c r="A520" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3">
+      <c r="A521" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C521" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3">
+      <c r="A522" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3">
+      <c r="A523" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3">
+      <c r="A524" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3">
+      <c r="A525" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B500" s="1" t="s">
+      <c r="B525" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3">
+      <c r="A526" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3">
+      <c r="A527" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3">
+      <c r="A528" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3">
+      <c r="A529" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C529" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3">
+      <c r="A530" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C530" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3">
+      <c r="A531" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C531" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3">
+      <c r="A532" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C532" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3">
+      <c r="A533" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C533" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3">
+      <c r="A534" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C534" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3">
+      <c r="A535" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C535" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3">
+      <c r="A536" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C536" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3">
+      <c r="A537" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C537" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3">
+      <c r="A538" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C538" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3">
+      <c r="A539" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B539" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C500" s="1" t="s">
+      <c r="C539" s="1" t="s">
         <v>401</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C500" xr:uid="{799D48F5-B989-4AA3-BCE2-AE0AB96B6C6B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C432">
-      <sortCondition ref="A2:A432"/>
-      <sortCondition ref="B2:B432"/>
-      <sortCondition ref="C2:C432"/>
+  <autoFilter ref="A1:C539" xr:uid="{799D48F5-B989-4AA3-BCE2-AE0AB96B6C6B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C453">
+      <sortCondition ref="A2:A453"/>
+      <sortCondition ref="B2:B453"/>
+      <sortCondition ref="C2:C453"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D500">
-    <sortCondition ref="A2:A500"/>
-    <sortCondition ref="B2:B500"/>
-    <sortCondition ref="C2:C500"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D539">
+    <sortCondition ref="A2:A539"/>
+    <sortCondition ref="B2:B539"/>
+    <sortCondition ref="C2:C539"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/CT Term Mapping Dictionary.xlsx
+++ b/config/CT Term Mapping Dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shirley.ho\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAD7697-A352-4DB8-9D78-6BA38ED87AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573D2B20-F08C-405D-909D-87534832E255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51DA8FFF-F53B-43BA-9BD3-FE23D4CF3F85}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="CT Term Mapping" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CT Term Mapping'!$A$1:$C$539</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CT Term Mapping'!$A$1:$C$548</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="560">
   <si>
     <t>CTVAL</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1909,6 +1909,35 @@
   <si>
     <t>Tumor Identification</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSTEST</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRGRESP</t>
+  </si>
+  <si>
+    <t>RSTESTCD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Response</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-target Response</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NTRGRESP</t>
+  </si>
+  <si>
+    <t>Overall Response</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OVRLRESP</t>
   </si>
 </sst>
 </file>
@@ -2334,7 +2363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799D48F5-B989-4AA3-BCE2-AE0AB96B6C6B}">
-  <dimension ref="A1:D539"/>
+  <dimension ref="A1:D548"/>
   <sheetFormatPr defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -7213,156 +7242,156 @@
     </row>
     <row r="443" spans="1:3">
       <c r="A443" s="1" t="s">
-        <v>47</v>
+        <v>552</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>18</v>
+        <v>556</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>19</v>
+        <v>556</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
-        <v>47</v>
+        <v>552</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>20</v>
+        <v>558</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>21</v>
+        <v>558</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" s="1" t="s">
-        <v>47</v>
+        <v>552</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>22</v>
+        <v>555</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>23</v>
+        <v>555</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" s="1" t="s">
-        <v>47</v>
+        <v>554</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>22</v>
+        <v>553</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>25</v>
+        <v>553</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" s="1" t="s">
-        <v>47</v>
+        <v>554</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>22</v>
+        <v>553</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>24</v>
+        <v>555</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" s="1" t="s">
-        <v>102</v>
+        <v>554</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>99</v>
+        <v>557</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>104</v>
+        <v>557</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" s="1" t="s">
-        <v>102</v>
+        <v>554</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>105</v>
+        <v>557</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>106</v>
+        <v>556</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" s="1" t="s">
-        <v>473</v>
+        <v>554</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>100</v>
+        <v>559</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>101</v>
+        <v>559</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" s="1" t="s">
-        <v>102</v>
+        <v>554</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>100</v>
+        <v>559</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>103</v>
+        <v>558</v>
       </c>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>462</v>
+        <v>19</v>
       </c>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" s="1" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>471</v>
+        <v>21</v>
       </c>
     </row>
     <row r="454" spans="1:3">
       <c r="A454" s="1" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>472</v>
+        <v>23</v>
       </c>
     </row>
     <row r="455" spans="1:3">
       <c r="A455" s="1" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="456" spans="1:3">
       <c r="A456" s="1" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -7370,296 +7399,296 @@
         <v>102</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="A458" s="1" t="s">
-        <v>534</v>
+        <v>102</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>538</v>
+        <v>105</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>538</v>
+        <v>106</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" s="1" t="s">
-        <v>534</v>
+        <v>473</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>540</v>
+        <v>100</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>540</v>
+        <v>101</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
-        <v>534</v>
+        <v>102</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>541</v>
+        <v>100</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>541</v>
+        <v>103</v>
       </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461" s="1" t="s">
-        <v>535</v>
+        <v>102</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>537</v>
+        <v>8</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>536</v>
+        <v>462</v>
       </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462" s="1" t="s">
-        <v>535</v>
+        <v>102</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>539</v>
+        <v>8</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>539</v>
+        <v>471</v>
       </c>
     </row>
     <row r="463" spans="1:3">
       <c r="A463" s="1" t="s">
-        <v>535</v>
+        <v>102</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>539</v>
+        <v>8</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>540</v>
+        <v>472</v>
       </c>
     </row>
     <row r="464" spans="1:3">
       <c r="A464" s="1" t="s">
-        <v>535</v>
+        <v>102</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>542</v>
+        <v>8</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>542</v>
+        <v>23</v>
       </c>
     </row>
     <row r="465" spans="1:3">
       <c r="A465" s="1" t="s">
-        <v>535</v>
+        <v>102</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>542</v>
+        <v>8</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>541</v>
+        <v>40</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" s="1" t="s">
-        <v>543</v>
+        <v>102</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>546</v>
+        <v>8</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>547</v>
+        <v>24</v>
       </c>
     </row>
     <row r="467" spans="1:3">
       <c r="A467" s="1" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
     </row>
     <row r="469" spans="1:3">
       <c r="A469" s="1" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="470" spans="1:3">
       <c r="A470" s="1" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" s="1" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="472" spans="1:3">
       <c r="A472" s="1" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
     </row>
     <row r="473" spans="1:3">
       <c r="A473" s="1" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
     </row>
     <row r="474" spans="1:3">
       <c r="A474" s="1" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
     </row>
     <row r="475" spans="1:3">
       <c r="A475" s="1" t="s">
-        <v>346</v>
+        <v>543</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>360</v>
+        <v>546</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>360</v>
+        <v>547</v>
       </c>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
-        <v>346</v>
+        <v>543</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>352</v>
+        <v>549</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>347</v>
+        <v>549</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477" s="1" t="s">
-        <v>346</v>
+        <v>543</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>382</v>
+        <v>551</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>380</v>
+        <v>551</v>
       </c>
     </row>
     <row r="478" spans="1:3">
       <c r="A478" s="1" t="s">
-        <v>346</v>
+        <v>544</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>387</v>
+        <v>545</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>387</v>
+        <v>545</v>
       </c>
     </row>
     <row r="479" spans="1:3">
       <c r="A479" s="1" t="s">
-        <v>346</v>
+        <v>544</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>354</v>
+        <v>545</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>355</v>
+        <v>546</v>
       </c>
     </row>
     <row r="480" spans="1:3">
       <c r="A480" s="1" t="s">
-        <v>346</v>
+        <v>544</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>354</v>
+        <v>548</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>353</v>
+        <v>548</v>
       </c>
     </row>
     <row r="481" spans="1:3">
       <c r="A481" s="1" t="s">
-        <v>346</v>
+        <v>544</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>384</v>
+        <v>548</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>384</v>
+        <v>549</v>
       </c>
     </row>
     <row r="482" spans="1:3">
       <c r="A482" s="1" t="s">
-        <v>346</v>
+        <v>544</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>357</v>
+        <v>550</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>358</v>
+        <v>550</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="A483" s="1" t="s">
-        <v>346</v>
+        <v>544</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>357</v>
+        <v>550</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>356</v>
+        <v>551</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -7667,10 +7696,10 @@
         <v>346</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -7678,10 +7707,10 @@
         <v>346</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -7689,10 +7718,10 @@
         <v>346</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -7700,10 +7729,10 @@
         <v>346</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -7711,10 +7740,10 @@
         <v>346</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -7722,10 +7751,10 @@
         <v>346</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -7733,10 +7762,10 @@
         <v>346</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -7744,10 +7773,10 @@
         <v>346</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -7755,10 +7784,10 @@
         <v>346</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -7766,10 +7795,10 @@
         <v>346</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -7777,10 +7806,10 @@
         <v>346</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -7788,10 +7817,10 @@
         <v>346</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -7799,10 +7828,10 @@
         <v>346</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -7810,10 +7839,10 @@
         <v>346</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -7821,10 +7850,10 @@
         <v>346</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -7832,10 +7861,10 @@
         <v>346</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>500</v>
+        <v>385</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>500</v>
+        <v>385</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -7843,10 +7872,10 @@
         <v>346</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -7854,10 +7883,10 @@
         <v>346</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>381</v>
+        <v>349</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -7865,10 +7894,10 @@
         <v>346</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -7876,10 +7905,10 @@
         <v>346</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -7887,10 +7916,10 @@
         <v>346</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -7898,10 +7927,10 @@
         <v>346</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -7909,10 +7938,10 @@
         <v>346</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -7920,10 +7949,10 @@
         <v>346</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -7931,285 +7960,285 @@
         <v>346</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>351</v>
+        <v>500</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>378</v>
+        <v>500</v>
       </c>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="510" spans="1:3">
       <c r="A510" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="511" spans="1:3">
       <c r="A511" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
     </row>
     <row r="512" spans="1:3">
       <c r="A512" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>390</v>
+        <v>362</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>390</v>
+        <v>361</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>383</v>
+        <v>350</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="514" spans="1:3">
       <c r="A514" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
     </row>
     <row r="515" spans="1:3">
       <c r="A515" s="1" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>393</v>
+        <v>350</v>
       </c>
     </row>
     <row r="516" spans="1:3">
       <c r="A516" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>394</v>
+        <v>351</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>403</v>
+        <v>351</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" s="1" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="519" spans="1:3">
       <c r="A519" s="1" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
     </row>
     <row r="520" spans="1:3">
       <c r="A520" s="1" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521" s="1" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
     </row>
     <row r="522" spans="1:3">
       <c r="A522" s="1" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
     </row>
     <row r="523" spans="1:3">
       <c r="A523" s="1" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
     </row>
     <row r="524" spans="1:3">
       <c r="A524" s="1" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
     </row>
     <row r="526" spans="1:3">
       <c r="A526" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="527" spans="1:3">
       <c r="A527" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="528" spans="1:3">
       <c r="A528" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="529" spans="1:3">
       <c r="A529" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="530" spans="1:3">
       <c r="A530" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="531" spans="1:3">
       <c r="A531" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="532" spans="1:3">
       <c r="A532" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -8217,10 +8246,10 @@
         <v>408</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -8228,10 +8257,10 @@
         <v>408</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -8239,10 +8268,10 @@
         <v>408</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -8250,10 +8279,10 @@
         <v>408</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -8261,10 +8290,10 @@
         <v>408</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -8272,24 +8301,123 @@
         <v>408</v>
       </c>
       <c r="B539" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C539" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3">
+      <c r="A540" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3">
+      <c r="A541" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C541" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3">
+      <c r="A542" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3">
+      <c r="A543" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3">
+      <c r="A544" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C544" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3">
+      <c r="A545" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C545" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3">
+      <c r="A546" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3">
+      <c r="A547" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C547" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3">
+      <c r="A548" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B548" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C539" s="1" t="s">
+      <c r="C548" s="1" t="s">
         <v>401</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C539" xr:uid="{799D48F5-B989-4AA3-BCE2-AE0AB96B6C6B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C453">
-      <sortCondition ref="A2:A453"/>
-      <sortCondition ref="B2:B453"/>
-      <sortCondition ref="C2:C453"/>
+  <autoFilter ref="A1:C548" xr:uid="{799D48F5-B989-4AA3-BCE2-AE0AB96B6C6B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C462">
+      <sortCondition ref="A2:A462"/>
+      <sortCondition ref="B2:B462"/>
+      <sortCondition ref="C2:C462"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D539">
-    <sortCondition ref="A2:A539"/>
-    <sortCondition ref="B2:B539"/>
-    <sortCondition ref="C2:C539"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D548">
+    <sortCondition ref="A2:A548"/>
+    <sortCondition ref="B2:B548"/>
+    <sortCondition ref="C2:C548"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/CT Term Mapping Dictionary.xlsx
+++ b/config/CT Term Mapping Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shirley.ho\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573D2B20-F08C-405D-909D-87534832E255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982C0441-E768-458B-BB10-53C3C65B4401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51DA8FFF-F53B-43BA-9BD3-FE23D4CF3F85}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51DA8FFF-F53B-43BA-9BD3-FE23D4CF3F85}"/>
   </bookViews>
   <sheets>
     <sheet name="CT Term Mapping" sheetId="1" r:id="rId1"/>
@@ -1911,17 +1911,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>RSTEST</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TRGRESP</t>
   </si>
   <si>
-    <t>RSTESTCD</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Response</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1938,6 +1930,14 @@
   </si>
   <si>
     <t>OVRLRESP</t>
+  </si>
+  <si>
+    <t>ONCRTS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ONCRTSCD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6637,101 +6637,101 @@
     </row>
     <row r="388" spans="1:3">
       <c r="A388" s="1" t="s">
-        <v>117</v>
+        <v>558</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>118</v>
+        <v>554</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>127</v>
+        <v>554</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" s="1" t="s">
-        <v>117</v>
+        <v>558</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>119</v>
+        <v>556</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>458</v>
+        <v>556</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" s="1" t="s">
-        <v>117</v>
+        <v>558</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>119</v>
+        <v>553</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>125</v>
+        <v>553</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" s="1" t="s">
-        <v>117</v>
+        <v>559</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>119</v>
+        <v>552</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>128</v>
+        <v>552</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" s="1" t="s">
-        <v>117</v>
+        <v>559</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>121</v>
+        <v>552</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" s="1" t="s">
-        <v>117</v>
+        <v>559</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>121</v>
+        <v>555</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>123</v>
+        <v>555</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" s="1" t="s">
-        <v>117</v>
+        <v>559</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>121</v>
+        <v>555</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>130</v>
+        <v>554</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
-        <v>117</v>
+        <v>559</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>120</v>
+        <v>557</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>460</v>
+        <v>557</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" s="1" t="s">
-        <v>117</v>
+        <v>559</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>120</v>
+        <v>557</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>124</v>
+        <v>556</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -6739,10 +6739,10 @@
         <v>117</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -6750,10 +6750,10 @@
         <v>117</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -6761,10 +6761,10 @@
         <v>117</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -6772,10 +6772,10 @@
         <v>117</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -6783,10 +6783,10 @@
         <v>117</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>23</v>
+        <v>459</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -6794,10 +6794,10 @@
         <v>117</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -6805,81 +6805,81 @@
         <v>117</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
     </row>
     <row r="404" spans="1:3">
       <c r="A404" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>35</v>
+        <v>460</v>
       </c>
     </row>
     <row r="405" spans="1:3">
       <c r="A405" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
     </row>
     <row r="406" spans="1:3">
       <c r="A406" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>37</v>
+        <v>129</v>
       </c>
     </row>
     <row r="407" spans="1:3">
       <c r="A407" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>38</v>
+        <v>461</v>
       </c>
     </row>
     <row r="408" spans="1:3">
       <c r="A408" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
     </row>
     <row r="409" spans="1:3">
       <c r="A409" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
     </row>
     <row r="410" spans="1:3">
       <c r="A410" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B410" s="1" t="s">
         <v>8</v>
@@ -6890,7 +6890,7 @@
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>8</v>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="412" spans="1:3">
       <c r="A412" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>8</v>
@@ -6915,109 +6915,109 @@
         <v>48</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>314</v>
+        <v>27</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>311</v>
+        <v>36</v>
       </c>
     </row>
     <row r="415" spans="1:3">
       <c r="A415" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>496</v>
+        <v>28</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>312</v>
+        <v>37</v>
       </c>
     </row>
     <row r="416" spans="1:3">
       <c r="A416" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>314</v>
+        <v>29</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>313</v>
+        <v>38</v>
       </c>
     </row>
     <row r="417" spans="1:3">
       <c r="A417" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>317</v>
+        <v>30</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>318</v>
+        <v>31</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>319</v>
+        <v>32</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>320</v>
+        <v>33</v>
       </c>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>321</v>
+        <v>8</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>322</v>
+        <v>23</v>
       </c>
     </row>
     <row r="420" spans="1:3">
       <c r="A420" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>503</v>
+        <v>8</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>504</v>
+        <v>40</v>
       </c>
     </row>
     <row r="421" spans="1:3">
       <c r="A421" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>327</v>
+        <v>8</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>328</v>
+        <v>24</v>
       </c>
     </row>
     <row r="422" spans="1:3">
       <c r="A422" s="1" t="s">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>325</v>
+        <v>34</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>326</v>
+        <v>39</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -7025,10 +7025,10 @@
         <v>310</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -7036,10 +7036,10 @@
         <v>310</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>331</v>
+        <v>496</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -7047,10 +7047,10 @@
         <v>310</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -7058,10 +7058,10 @@
         <v>310</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -7069,10 +7069,10 @@
         <v>310</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -7080,10 +7080,10 @@
         <v>310</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>501</v>
+        <v>321</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>501</v>
+        <v>322</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -7091,10 +7091,10 @@
         <v>310</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -7102,10 +7102,10 @@
         <v>310</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -7113,10 +7113,10 @@
         <v>310</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -7124,10 +7124,10 @@
         <v>310</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -7135,10 +7135,10 @@
         <v>310</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -7146,10 +7146,10 @@
         <v>310</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -7157,10 +7157,10 @@
         <v>310</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -7168,10 +7168,10 @@
         <v>310</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>505</v>
+        <v>335</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>506</v>
+        <v>336</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -7179,10 +7179,10 @@
         <v>310</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>8</v>
+        <v>501</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>25</v>
+        <v>501</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -7190,10 +7190,10 @@
         <v>310</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>8</v>
+        <v>501</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>24</v>
+        <v>502</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -7201,142 +7201,142 @@
         <v>310</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
-        <v>454</v>
+        <v>310</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>455</v>
+        <v>323</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>455</v>
+        <v>324</v>
       </c>
     </row>
     <row r="441" spans="1:3">
       <c r="A441" s="1" t="s">
-        <v>456</v>
+        <v>310</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>457</v>
+        <v>339</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>455</v>
+        <v>340</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442" s="1" t="s">
-        <v>456</v>
+        <v>310</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>457</v>
+        <v>341</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>457</v>
+        <v>342</v>
       </c>
     </row>
     <row r="443" spans="1:3">
       <c r="A443" s="1" t="s">
-        <v>552</v>
+        <v>310</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>556</v>
+        <v>315</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>556</v>
+        <v>316</v>
       </c>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
-        <v>552</v>
+        <v>310</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>558</v>
+        <v>315</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>558</v>
+        <v>343</v>
       </c>
     </row>
     <row r="445" spans="1:3">
       <c r="A445" s="1" t="s">
-        <v>552</v>
+        <v>310</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>555</v>
+        <v>505</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>555</v>
+        <v>506</v>
       </c>
     </row>
     <row r="446" spans="1:3">
       <c r="A446" s="1" t="s">
-        <v>554</v>
+        <v>310</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>553</v>
+        <v>8</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>553</v>
+        <v>25</v>
       </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447" s="1" t="s">
-        <v>554</v>
+        <v>310</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>553</v>
+        <v>8</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>555</v>
+        <v>24</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448" s="1" t="s">
-        <v>554</v>
+        <v>310</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>557</v>
+        <v>344</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>557</v>
+        <v>345</v>
       </c>
     </row>
     <row r="449" spans="1:3">
       <c r="A449" s="1" t="s">
-        <v>554</v>
+        <v>454</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>557</v>
+        <v>455</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>556</v>
+        <v>455</v>
       </c>
     </row>
     <row r="450" spans="1:3">
       <c r="A450" s="1" t="s">
-        <v>554</v>
+        <v>456</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>559</v>
+        <v>457</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>559</v>
+        <v>455</v>
       </c>
     </row>
     <row r="451" spans="1:3">
       <c r="A451" s="1" t="s">
-        <v>554</v>
+        <v>456</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>559</v>
+        <v>457</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>558</v>
+        <v>457</v>
       </c>
     </row>
     <row r="452" spans="1:3">
